--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N85_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N85_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>50.92545736463949</v>
+        <v>8.275386821753917</v>
       </c>
       <c r="D2" t="n">
-        <v>51.04566282445806</v>
+        <v>8.294920208974435</v>
       </c>
       <c r="E2" t="n">
-        <v>16.45781917066417</v>
+        <v>2.674395615232928</v>
       </c>
       <c r="F2" t="n">
-        <v>16.55454189052287</v>
+        <v>2.690113057209966</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>39.62699815104638</v>
+        <v>6.439387199545036</v>
       </c>
       <c r="D3" t="n">
-        <v>39.84211756191564</v>
+        <v>6.474344103811291</v>
       </c>
       <c r="E3" t="n">
-        <v>16.45781917066417</v>
+        <v>2.674395615232928</v>
       </c>
       <c r="F3" t="n">
-        <v>16.55454189052287</v>
+        <v>2.690113057209966</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>24.0824834381405</v>
+        <v>3.913403558697832</v>
       </c>
       <c r="D4" t="n">
-        <v>24.07062944204867</v>
+        <v>3.911477284332908</v>
       </c>
       <c r="E4" t="n">
-        <v>16.45781917066417</v>
+        <v>2.674395615232928</v>
       </c>
       <c r="F4" t="n">
-        <v>16.55454189052287</v>
+        <v>2.690113057209966</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>31.2639016969952</v>
+        <v>5.080384025761719</v>
       </c>
       <c r="D5" t="n">
-        <v>31.75166375995651</v>
+        <v>5.159645360992933</v>
       </c>
       <c r="E5" t="n">
-        <v>16.45781917066417</v>
+        <v>2.674395615232928</v>
       </c>
       <c r="F5" t="n">
-        <v>16.55454189052287</v>
+        <v>2.690113057209966</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>21.67530305473339</v>
+        <v>3.522236746394177</v>
       </c>
       <c r="D6" t="n">
-        <v>21.220442553496</v>
+        <v>3.4483219149431</v>
       </c>
       <c r="E6" t="n">
-        <v>16.45781917066417</v>
+        <v>2.674395615232928</v>
       </c>
       <c r="F6" t="n">
-        <v>16.55454189052287</v>
+        <v>2.690113057209966</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>3.771045620924533</v>
+        <v>0.6127949134002366</v>
       </c>
       <c r="D7" t="n">
-        <v>3.638039538052109</v>
+        <v>0.5911814249334677</v>
       </c>
       <c r="E7" t="n">
-        <v>16.45781917066417</v>
+        <v>2.674395615232928</v>
       </c>
       <c r="F7" t="n">
-        <v>16.55454189052287</v>
+        <v>2.690113057209966</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>37.27985316591986</v>
+        <v>6.057976139461977</v>
       </c>
       <c r="D8" t="n">
-        <v>36.77266022897517</v>
+        <v>5.975557287208465</v>
       </c>
       <c r="E8" t="n">
-        <v>16.45781917066417</v>
+        <v>2.674395615232928</v>
       </c>
       <c r="F8" t="n">
-        <v>16.55454189052287</v>
+        <v>2.690113057209966</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>34.98507240303523</v>
+        <v>5.685074265493226</v>
       </c>
       <c r="D9" t="n">
-        <v>35.48773705407985</v>
+        <v>5.766757271287976</v>
       </c>
       <c r="E9" t="n">
-        <v>16.45781917066417</v>
+        <v>2.674395615232928</v>
       </c>
       <c r="F9" t="n">
-        <v>16.55454189052287</v>
+        <v>2.690113057209966</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>25.67251735582039</v>
+        <v>4.171784070320814</v>
       </c>
       <c r="D10" t="n">
-        <v>25.1699331470124</v>
+        <v>4.090114136389515</v>
       </c>
       <c r="E10" t="n">
-        <v>16.45781917066417</v>
+        <v>2.674395615232928</v>
       </c>
       <c r="F10" t="n">
-        <v>16.55454189052287</v>
+        <v>2.690113057209966</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>15.82226395068389</v>
+        <v>2.571117891986133</v>
       </c>
       <c r="D11" t="n">
-        <v>15.44564902096037</v>
+        <v>2.50991796590606</v>
       </c>
       <c r="E11" t="n">
-        <v>16.45781917066417</v>
+        <v>2.674395615232928</v>
       </c>
       <c r="F11" t="n">
-        <v>16.55454189052287</v>
+        <v>2.690113057209966</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>17.40895183255605</v>
+        <v>2.828954672790359</v>
       </c>
       <c r="D12" t="n">
-        <v>17.19398914610019</v>
+        <v>2.794023236241281</v>
       </c>
       <c r="E12" t="n">
-        <v>16.45781917066417</v>
+        <v>2.674395615232928</v>
       </c>
       <c r="F12" t="n">
-        <v>16.55454189052287</v>
+        <v>2.690113057209966</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>24.16975677987485</v>
+        <v>3.927585476729664</v>
       </c>
       <c r="D13" t="n">
-        <v>24.40570267224619</v>
+        <v>3.965926684240005</v>
       </c>
       <c r="E13" t="n">
-        <v>16.45781917066417</v>
+        <v>2.674395615232928</v>
       </c>
       <c r="F13" t="n">
-        <v>16.55454189052287</v>
+        <v>2.690113057209966</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>31.97762551040799</v>
+        <v>5.196364145441299</v>
       </c>
       <c r="D14" t="n">
-        <v>31.83460380693841</v>
+        <v>5.173123118627492</v>
       </c>
       <c r="E14" t="n">
-        <v>16.45781917066417</v>
+        <v>2.674395615232928</v>
       </c>
       <c r="F14" t="n">
-        <v>16.55454189052287</v>
+        <v>2.690113057209966</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>46.95986919261174</v>
+        <v>7.630978743799409</v>
       </c>
       <c r="D15" t="n">
-        <v>47.01177548685033</v>
+        <v>7.639413516613179</v>
       </c>
       <c r="E15" t="n">
-        <v>16.45781917066417</v>
+        <v>2.674395615232928</v>
       </c>
       <c r="F15" t="n">
-        <v>16.55454189052287</v>
+        <v>2.690113057209966</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>53.15310206351823</v>
+        <v>8.637379085321713</v>
       </c>
       <c r="D16" t="n">
-        <v>53.33115145676027</v>
+        <v>8.666312111723546</v>
       </c>
       <c r="E16" t="n">
-        <v>16.45781917066417</v>
+        <v>2.674395615232928</v>
       </c>
       <c r="F16" t="n">
-        <v>16.55454189052287</v>
+        <v>2.690113057209966</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>62.23519918357298</v>
+        <v>10.11321986733061</v>
       </c>
       <c r="D17" t="n">
-        <v>62.11426916087851</v>
+        <v>10.09356873864276</v>
       </c>
       <c r="E17" t="n">
-        <v>16.45781917066417</v>
+        <v>2.674395615232928</v>
       </c>
       <c r="F17" t="n">
-        <v>16.55454189052287</v>
+        <v>2.690113057209966</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>65.61983841651329</v>
+        <v>10.66322374268341</v>
       </c>
       <c r="D18" t="n">
-        <v>65.69328721454944</v>
+        <v>10.67515917236429</v>
       </c>
       <c r="E18" t="n">
-        <v>16.45781917066417</v>
+        <v>2.674395615232928</v>
       </c>
       <c r="F18" t="n">
-        <v>16.55454189052287</v>
+        <v>2.690113057209966</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
